--- a/forms/trg/Formulir_TRG_biofoodpack.xlsx
+++ b/forms/trg/Formulir_TRG_biofoodpack.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B23)</f>
+        <f>COUNTA(Anggota!B5:B24)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F23)</f>
+        <f>COUNTA(Anggota!F5:F24)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,33 +925,37 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. rer.nat. Zainal, M.FoodTech</t>
+          <t>Dr. Adiansyah Syarifuddin, STP, MSi</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="n"/>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Edible Film &amp; Coating, Food Packaging</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-4205-1805</t>
+        </is>
+      </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>5976059</t>
+          <t>6005720</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57216221263</t>
+          <t>57200303550</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -966,12 +970,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof.Ir. Andi Dirpan, STP, PhD</t>
+          <t>Dr. rer.nat. Zainal, M.FoodTech</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -984,19 +988,15 @@
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-0167-7016</t>
-        </is>
-      </c>
+      <c r="J6" s="12" t="n"/>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>5976161</t>
+          <t>5976059</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57199234020</t>
+          <t>57216221263</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Mulyati Muhammad Tahir, MSi</t>
+          <t>Prof.Ir. Andi Dirpan, STP, PhD</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1029,15 +1029,19 @@
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-0167-7016</t>
+        </is>
+      </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6020073</t>
+          <t>5976161</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57188875144</t>
+          <t>57199234020</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1052,37 +1056,33 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Intan Syafinaz Binti Mohamed Amin Tawakkal</t>
+          <t>Prof. Dr. Ir. Mulyati Muhammad Tahir, MSi</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Universiti Putra Malaysia</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>Food Packaging &amp; Packaging Engineering</t>
-        </is>
-      </c>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="n"/>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-2796-2608</t>
-        </is>
-      </c>
-      <c r="K8" s="12" t="n"/>
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>6020073</t>
+        </is>
+      </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>37049274400</t>
+          <t>57188875144</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1097,31 +1097,39 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>REZA ARIANTO SULTAN</t>
+          <t>Dr. Intan Syafinaz Binti Mohamed Amin Tawakkal</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Universitas Sulawesi Barat</t>
+          <t>Universiti Putra Malaysia</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Food Packaging</t>
+          <t>Food Packaging &amp; Packaging Engineering</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-2796-2608</t>
+        </is>
+      </c>
       <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>37049274400</t>
+        </is>
+      </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1134,22 +1142,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Ahmad Azhari Arif</t>
+          <t>REZA ARIANTO SULTAN</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Universitas Sulawesi Barat</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Food Science &amp; Technology</t>
+          <t>Food Packaging</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1171,12 +1179,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Firadillah Tsani Arif</t>
+          <t>Ahmad Azhari Arif</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1206,10 +1214,26 @@
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="11" t="n"/>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Firadillah Tsani Arif</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Food Science &amp; Technology</t>
+        </is>
+      </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
@@ -1217,7 +1241,11 @@
       <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1406,15 +1434,32 @@
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="12" t="n"/>
     </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
